--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -2351,7 +2351,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11888,7 +11888,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13850,7 +13850,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14092,7 +14092,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -15840,7 +15840,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -17143,7 +17143,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17797,7 +17797,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18209,7 +18209,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -18451,7 +18451,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -20606,7 +20606,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -20848,7 +20848,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21260,7 +21260,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21502,7 +21502,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21914,7 +21914,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -22156,7 +22156,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22568,7 +22568,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22810,7 +22810,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23222,7 +23222,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23865,7 +23865,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -25053,7 +25053,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25460,7 +25460,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25702,7 +25702,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -26114,7 +26114,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26356,7 +26356,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -26768,7 +26768,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27010,7 +27010,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -27422,7 +27422,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -28065,7 +28065,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -29253,7 +29253,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -29660,7 +29660,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29902,7 +29902,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -30314,7 +30314,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -30556,7 +30556,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -30968,7 +30968,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -31210,7 +31210,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -31622,7 +31622,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -32265,7 +32265,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -33453,7 +33453,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -33860,7 +33860,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -34102,7 +34102,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -2351,7 +2351,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11888,7 +11888,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13850,7 +13850,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14092,7 +14092,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -15840,7 +15840,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -17143,7 +17143,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17797,7 +17797,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18209,7 +18209,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -18451,7 +18451,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -20606,7 +20606,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -20848,7 +20848,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21260,7 +21260,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21502,7 +21502,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21914,7 +21914,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -22156,7 +22156,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22568,7 +22568,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22810,7 +22810,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23222,7 +23222,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23865,7 +23865,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -25053,7 +25053,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25460,7 +25460,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25702,7 +25702,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -26114,7 +26114,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26356,7 +26356,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -26768,7 +26768,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27010,7 +27010,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -27422,7 +27422,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -28065,7 +28065,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -29009,16 +29009,16 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O138" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>0.02607415467862137</v>
+        <v>0.03041984712505827</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -29171,10 +29171,10 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O139" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
@@ -29253,7 +29253,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -29660,7 +29660,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29902,7 +29902,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -30314,7 +30314,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -30556,7 +30556,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -30968,7 +30968,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -31210,7 +31210,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -31622,7 +31622,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -32265,7 +32265,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -33453,7 +33453,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -33860,7 +33860,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -34102,7 +34102,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -34370,7 +34370,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -927,9 +927,6 @@
       <c r="O3" t="n">
         <v>8</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1320,9 +1317,6 @@
       <c r="O5" t="n">
         <v>10</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.1778809170864138</v>
       </c>
@@ -1716,9 +1710,6 @@
       <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -2361,7 +2352,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2511,9 +2502,6 @@
       <c r="P11" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -2923,9 +2911,6 @@
       <c r="P13" t="n">
         <v>10</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.002865038132769385</v>
       </c>
@@ -3577,9 +3562,6 @@
       <c r="P16" t="n">
         <v>17</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.004870564825707955</v>
       </c>
@@ -4231,9 +4213,6 @@
       <c r="P19" t="n">
         <v>14</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.00401105338587714</v>
       </c>
@@ -4885,9 +4864,6 @@
       <c r="P22" t="n">
         <v>19</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.005443572452261832</v>
       </c>
@@ -5698,9 +5674,6 @@
       <c r="O26" t="n">
         <v>10</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6091,9 +6064,6 @@
       <c r="O28" t="n">
         <v>6</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.1067285502518482</v>
       </c>
@@ -6487,9 +6457,6 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -7132,7 +7099,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7282,9 +7249,6 @@
       <c r="P34" t="n">
         <v>18</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.005157068638984894</v>
       </c>
@@ -7936,9 +7900,6 @@
       <c r="P37" t="n">
         <v>26</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.007449099145200401</v>
       </c>
@@ -8590,9 +8551,6 @@
       <c r="P40" t="n">
         <v>22</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.006303083892092647</v>
       </c>
@@ -9244,9 +9202,6 @@
       <c r="P43" t="n">
         <v>14</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.00401105338587714</v>
       </c>
@@ -10057,9 +10012,6 @@
       <c r="O47" t="n">
         <v>8</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="S47" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10450,9 +10402,6 @@
       <c r="O49" t="n">
         <v>6</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.1067285502518482</v>
       </c>
@@ -10846,9 +10795,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -11491,7 +11437,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -11641,9 +11587,6 @@
       <c r="P55" t="n">
         <v>17</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.004870564825707955</v>
       </c>
@@ -12295,9 +12238,6 @@
       <c r="P58" t="n">
         <v>22</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.006303083892092647</v>
       </c>
@@ -12949,9 +12889,6 @@
       <c r="P61" t="n">
         <v>13</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.003724549572600201</v>
       </c>
@@ -13603,9 +13540,6 @@
       <c r="P64" t="n">
         <v>14</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.00401105338587714</v>
       </c>
@@ -14254,9 +14188,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -14416,9 +14347,6 @@
       <c r="O68" t="n">
         <v>8</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14809,9 +14737,6 @@
       <c r="O70" t="n">
         <v>8</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.142304733669131</v>
       </c>
@@ -15205,9 +15130,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -15601,9 +15523,6 @@
       <c r="O74" t="n">
         <v>15</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.06518538669655344</v>
       </c>
@@ -15850,7 +15769,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -16000,9 +15919,6 @@
       <c r="P76" t="n">
         <v>9</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.002578534319492447</v>
       </c>
@@ -16654,9 +16570,6 @@
       <c r="P79" t="n">
         <v>17</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.004870564825707955</v>
       </c>
@@ -17308,9 +17221,6 @@
       <c r="P82" t="n">
         <v>12</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.003438045759323263</v>
       </c>
@@ -17962,9 +17872,6 @@
       <c r="P85" t="n">
         <v>19</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.005443572452261832</v>
       </c>
@@ -18613,9 +18520,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -18775,9 +18679,6 @@
       <c r="O89" t="n">
         <v>8</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="S89" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19168,9 +19069,6 @@
       <c r="O91" t="n">
         <v>3</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.05336427512592412</v>
       </c>
@@ -19564,9 +19462,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -19960,9 +19855,6 @@
       <c r="O95" t="n">
         <v>17</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.07387677158942724</v>
       </c>
@@ -20209,7 +20101,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -20359,9 +20251,6 @@
       <c r="P97" t="n">
         <v>20</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.00573007626553877</v>
       </c>
@@ -21013,9 +20902,6 @@
       <c r="P100" t="n">
         <v>11</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.003151541946046324</v>
       </c>
@@ -21667,9 +21553,6 @@
       <c r="P103" t="n">
         <v>17</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.004870564825707955</v>
       </c>
@@ -22321,9 +22204,6 @@
       <c r="P106" t="n">
         <v>9</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.002578534319492447</v>
       </c>
@@ -22975,9 +22855,6 @@
       <c r="P109" t="n">
         <v>10</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.002865038132769385</v>
       </c>
@@ -23626,9 +23503,6 @@
       <c r="O112" t="n">
         <v>5</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.01836405909759895</v>
       </c>
@@ -24022,9 +23896,6 @@
       <c r="O114" t="n">
         <v>8</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.142304733669131</v>
       </c>
@@ -24418,9 +24289,6 @@
       <c r="O116" t="n">
         <v>1</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -24814,9 +24682,6 @@
       <c r="O118" t="n">
         <v>7</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.03041984712505827</v>
       </c>
@@ -25063,7 +24928,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -25213,9 +25078,6 @@
       <c r="P120" t="n">
         <v>12</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.003438045759323263</v>
       </c>
@@ -25867,9 +25729,6 @@
       <c r="P123" t="n">
         <v>17</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.004870564825707955</v>
       </c>
@@ -26521,9 +26380,6 @@
       <c r="P126" t="n">
         <v>17</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.004870564825707955</v>
       </c>
@@ -27175,9 +27031,6 @@
       <c r="P129" t="n">
         <v>17</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.004870564825707955</v>
       </c>
@@ -27826,9 +27679,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -28222,9 +28072,6 @@
       <c r="O134" t="n">
         <v>12</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.2134571005036965</v>
       </c>
@@ -28618,9 +28465,6 @@
       <c r="O136" t="n">
         <v>3</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.05306927477386519</v>
       </c>
@@ -29014,9 +28858,6 @@
       <c r="O138" t="n">
         <v>7</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.03041984712505827</v>
       </c>
@@ -29263,7 +29104,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -29413,9 +29254,6 @@
       <c r="P140" t="n">
         <v>14</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.00401105338587714</v>
       </c>
@@ -30067,9 +29905,6 @@
       <c r="P143" t="n">
         <v>15</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.004297557199154077</v>
       </c>
@@ -30721,9 +30556,6 @@
       <c r="P146" t="n">
         <v>25</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.007162595331923463</v>
       </c>
@@ -31375,9 +31207,6 @@
       <c r="P149" t="n">
         <v>23</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.006589587705369587</v>
       </c>
@@ -32026,9 +31855,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -32422,9 +32248,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -32818,9 +32641,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -33209,16 +33029,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O158" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R158" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -33371,10 +33188,10 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U159" t="inlineStr">
         <is>
@@ -33463,7 +33280,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -33613,9 +33430,6 @@
       <c r="P160" t="n">
         <v>18</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.005157068638984894</v>
       </c>
@@ -34187,6 +34001,657 @@
         </is>
       </c>
       <c r="BC162" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>13</v>
+      </c>
+      <c r="O163" t="n">
+        <v>13</v>
+      </c>
+      <c r="P163" t="n">
+        <v>13</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0.003724549572600201</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>13</v>
+      </c>
+      <c r="O164" t="n">
+        <v>13</v>
+      </c>
+      <c r="P164" t="n">
+        <v>13</v>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+        </is>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN164" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>2</v>
+      </c>
+      <c r="O165" t="n">
+        <v>2</v>
+      </c>
+      <c r="P165" t="n">
+        <v>2</v>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Probable</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -34225,7 +34690,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -34308,7 +34773,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -34318,7 +34783,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -34338,7 +34803,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -34370,7 +34835,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>665</v>
+        <v>679</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -33029,13 +33029,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O158" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R158" t="n">
-        <v>0.008691384892873792</v>
+        <v>0.01738276978574758</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -33188,10 +33188,10 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O159" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U159" t="inlineStr">
         <is>
@@ -34835,7 +34835,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -10007,10 +10007,10 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -10163,10 +10163,10 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -14342,10 +14342,10 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O68" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -14498,10 +14498,10 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O69" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -18674,10 +18674,10 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O89" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -18830,10 +18830,10 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O90" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
@@ -23852,12 +23852,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -23891,22 +23891,19 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O114" t="n">
-        <v>8</v>
-      </c>
-      <c r="R114" t="n">
-        <v>0.142304733669131</v>
+        <v>10</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_140</t>
+          <t>SER_CA_ON_PHO_IDTO_ACUTE_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -23926,12 +23923,12 @@
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_140</t>
+          <t>SER_CA_ON_PHO_IDTO_ACUTE_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT114" t="n">
@@ -23939,47 +23936,47 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -24011,12 +24008,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -24050,24 +24047,24 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O115" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_140</t>
+          <t>SER_CA_ON_PHO_IDTO_ACUTE_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_140</t>
+          <t>SER_CA_ON_PHO_IDTO_ACUTE_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X115" t="inlineStr">
@@ -24082,7 +24079,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -24097,7 +24094,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD115" t="inlineStr">
@@ -24132,17 +24129,17 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
+          <t>PHO IDTO current-year monthly preliminary acute hepatitis B notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -24160,12 +24157,12 @@
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_140</t>
+          <t>SER_CA_ON_PHO_IDTO_ACUTE_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT115" t="n">
@@ -24173,47 +24170,47 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -24245,12 +24242,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -24284,13 +24281,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O116" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R116" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.142304733669131</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -24299,7 +24296,7 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_202_MONTHLY</t>
+          <t>SER_FI_THL_TTR_140</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -24319,12 +24316,12 @@
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_202_MONTHLY</t>
+          <t>SER_FI_THL_TTR_140</t>
         </is>
       </c>
       <c r="AT116" t="n">
@@ -24332,47 +24329,47 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24404,12 +24401,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -24443,29 +24440,29 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O117" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_202_MONTHLY</t>
+          <t>SER_FI_THL_TTR_140</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_202_MONTHLY</t>
+          <t>SER_FI_THL_TTR_140</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>Hepatitt B, akutt</t>
+          <t>Hepatitis B, acute</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
@@ -24490,7 +24487,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD117" t="inlineStr">
@@ -24525,17 +24522,17 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS acute category.</t>
+          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24553,12 +24550,12 @@
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_202_MONTHLY</t>
+          <t>SER_FI_THL_TTR_140</t>
         </is>
       </c>
       <c r="AT117" t="n">
@@ -24566,47 +24563,47 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24638,12 +24635,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -24677,13 +24674,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O118" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R118" t="n">
-        <v>0.03041984712505827</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -24692,7 +24689,7 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
+          <t>SER_NO_FHI_202_MONTHLY</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -24717,7 +24714,7 @@
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
+          <t>SER_NO_FHI_202_MONTHLY</t>
         </is>
       </c>
       <c r="AT118" t="n">
@@ -24730,42 +24727,42 @@
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24797,12 +24794,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -24836,29 +24833,29 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O119" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
+          <t>SER_NO_FHI_202_MONTHLY</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
+          <t>SER_NO_FHI_202_MONTHLY</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>急性病毒性Ｂ型肝炎</t>
+          <t>Hepatitt B, akutt</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
@@ -24868,7 +24865,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -24883,7 +24880,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr">
@@ -24898,7 +24895,7 @@
       </c>
       <c r="AF119" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG119" t="inlineStr">
@@ -24918,17 +24915,17 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Acute hepatitis B, code 0703.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS acute category.</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24951,7 +24948,7 @@
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
+          <t>SER_NO_FHI_202_MONTHLY</t>
         </is>
       </c>
       <c r="AT119" t="n">
@@ -24964,42 +24961,42 @@
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25031,12 +25028,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -25061,7 +25058,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -25070,16 +25067,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O120" t="n">
-        <v>12</v>
-      </c>
-      <c r="P120" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R120" t="n">
-        <v>0.003438045759323263</v>
+        <v>0.03041984712505827</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -25088,85 +25082,80 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
         </is>
       </c>
       <c r="AT120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -25198,12 +25187,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -25228,7 +25217,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -25237,32 +25226,29 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O121" t="n">
-        <v>12</v>
-      </c>
-      <c r="P121" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>Hepatitis B, acute, Confirmed</t>
+          <t>急性病毒性Ｂ型肝炎</t>
         </is>
       </c>
       <c r="Y121" t="inlineStr">
@@ -25277,7 +25263,7 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
@@ -25287,7 +25273,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD121" t="inlineStr">
@@ -25327,12 +25313,12 @@
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+          <t>Acute hepatitis B, code 0703.</t>
         </is>
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -25340,75 +25326,70 @@
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
         </is>
       </c>
       <c r="AT121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -25435,7 +25416,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -25479,106 +25460,31 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O122" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P122" t="n">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.003438045759323263</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>Hepatitis B, acute, Probable</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD122" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG122" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN122" t="b">
-        <v>0</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -25677,7 +25583,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -25712,7 +25618,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -25721,31 +25627,106 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="O123" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="P123" t="n">
-        <v>17</v>
-      </c>
-      <c r="R123" t="n">
-        <v>0.004870564825707955</v>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>12</v>
       </c>
       <c r="U123" t="inlineStr">
         <is>
           <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>1</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -25879,7 +25860,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -25888,22 +25869,22 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="O124" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="P124" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
@@ -25913,7 +25894,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>Hepatitis B, acute, Confirmed</t>
+          <t>Hepatitis B, acute, Probable</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
@@ -25978,7 +25959,7 @@
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
         </is>
       </c>
       <c r="AM124" t="inlineStr">
@@ -25987,7 +25968,7 @@
         </is>
       </c>
       <c r="AN124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -26086,7 +26067,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -26130,106 +26111,31 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="O125" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="P125" t="n">
-        <v>5</v>
+        <v>17</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.004870564825707955</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X125" t="inlineStr">
-        <is>
-          <t>Hepatitis B, acute, Probable</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD125" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE125" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF125" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG125" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN125" t="b">
-        <v>0</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -26328,7 +26234,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -26363,7 +26269,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -26380,23 +26286,98 @@
       <c r="P126" t="n">
         <v>17</v>
       </c>
-      <c r="R126" t="n">
-        <v>0.004870564825707955</v>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U126" t="inlineStr">
         <is>
           <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN126" t="b">
+        <v>1</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -26530,7 +26511,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -26539,22 +26520,22 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="O127" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="P127" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
@@ -26564,7 +26545,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>Hepatitis B, acute, Confirmed</t>
+          <t>Hepatitis B, acute, Probable</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
@@ -26629,7 +26610,7 @@
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
@@ -26638,7 +26619,7 @@
         </is>
       </c>
       <c r="AN127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -26737,7 +26718,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -26781,106 +26762,31 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="O128" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="P128" t="n">
-        <v>8</v>
+        <v>17</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.004870564825707955</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>Hepatitis B, acute, Probable</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD128" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE128" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF128" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG128" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
-        </is>
-      </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN128" t="b">
-        <v>0</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -26979,7 +26885,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -27014,7 +26920,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -27031,23 +26937,98 @@
       <c r="P129" t="n">
         <v>17</v>
       </c>
-      <c r="R129" t="n">
-        <v>0.004870564825707955</v>
-      </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U129" t="inlineStr">
         <is>
           <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN129" t="b">
+        <v>1</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -27181,7 +27162,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -27190,22 +27171,22 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="O130" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="P130" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V130" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W130" t="inlineStr">
@@ -27215,7 +27196,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>Hepatitis B, acute, Confirmed</t>
+          <t>Hepatitis B, acute, Probable</t>
         </is>
       </c>
       <c r="Y130" t="inlineStr">
@@ -27280,7 +27261,7 @@
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
         </is>
       </c>
       <c r="AM130" t="inlineStr">
@@ -27289,7 +27270,7 @@
         </is>
       </c>
       <c r="AN130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -27388,7 +27369,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -27432,106 +27413,31 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="O131" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="P131" t="n">
-        <v>5</v>
+        <v>17</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.004870564825707955</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W131" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X131" t="inlineStr">
-        <is>
-          <t>Hepatitis B, acute, Probable</t>
-        </is>
-      </c>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD131" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE131" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF131" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG131" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
-        </is>
-      </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN131" t="b">
-        <v>0</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -27630,17 +27536,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -27665,37 +27571,115 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
-      </c>
-      <c r="R132" t="n">
-        <v>0</v>
-      </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="P132" t="n">
+        <v>17</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_NEW</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN132" t="b">
+        <v>1</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -27704,7 +27688,7 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
@@ -27712,57 +27696,62 @@
           <t>legacy_gap_fill</t>
         </is>
       </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_NEW</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AT132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27794,12 +27783,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -27824,113 +27813,116 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N133" t="n">
+        <v>5</v>
+      </c>
+      <c r="O133" t="n">
+        <v>5</v>
+      </c>
+      <c r="P133" t="n">
+        <v>5</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Probable</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN133" t="b">
         <v>0</v>
       </c>
-      <c r="O133" t="n">
-        <v>0</v>
-      </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>SER_AU_HEPATITIS_B_NEW</t>
-        </is>
-      </c>
-      <c r="V133" t="inlineStr">
-        <is>
-          <t>SER_AU_HEPATITIS_B_NEW</t>
-        </is>
-      </c>
-      <c r="W133" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X133" t="inlineStr">
-        <is>
-          <t>Hepatitis B (newly acquired)</t>
-        </is>
-      </c>
-      <c r="Y133" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD133" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE133" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF133" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG133" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ133" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK133" t="inlineStr">
-        <is>
-          <t>Newly acquired hepatitis B, separate from unspecified hepatitis B.</t>
-        </is>
-      </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN133" t="b">
-        <v>1</v>
-      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>mixed</t>
@@ -27938,7 +27930,7 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
@@ -27946,57 +27938,62 @@
           <t>legacy_gap_fill</t>
         </is>
       </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS133" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_NEW</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AT133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28028,12 +28025,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -28067,13 +28064,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>0.2134571005036965</v>
+        <v>0</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -28082,7 +28079,7 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_140</t>
+          <t>SER_AU_HEPATITIS_B_NEW</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -28092,7 +28089,7 @@
       </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
@@ -28102,12 +28099,12 @@
       </c>
       <c r="AQ134" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_140</t>
+          <t>SER_AU_HEPATITIS_B_NEW</t>
         </is>
       </c>
       <c r="AT134" t="n">
@@ -28115,47 +28112,47 @@
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -28187,12 +28184,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -28226,29 +28223,29 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_140</t>
+          <t>SER_AU_HEPATITIS_B_NEW</t>
         </is>
       </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_140</t>
+          <t>SER_AU_HEPATITIS_B_NEW</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_AU_NINDSS</t>
         </is>
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>Hepatitis B, acute</t>
+          <t>Hepatitis B (newly acquired)</t>
         </is>
       </c>
       <c r="Y135" t="inlineStr">
@@ -28258,7 +28255,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -28273,7 +28270,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:AU:national</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
@@ -28288,7 +28285,7 @@
       </c>
       <c r="AF135" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG135" t="inlineStr">
@@ -28308,17 +28305,17 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
+          <t>Newly acquired hepatitis B, separate from unspecified hepatitis B.</t>
         </is>
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -28326,7 +28323,7 @@
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
@@ -28336,12 +28333,12 @@
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_140</t>
+          <t>SER_AU_HEPATITIS_B_NEW</t>
         </is>
       </c>
       <c r="AT135" t="n">
@@ -28349,47 +28346,47 @@
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -28421,12 +28418,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -28460,13 +28457,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O136" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R136" t="n">
-        <v>0.05306927477386519</v>
+        <v>0.2134571005036965</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -28475,7 +28472,7 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_202_MONTHLY</t>
+          <t>SER_FI_THL_TTR_140</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -28495,12 +28492,12 @@
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_202_MONTHLY</t>
+          <t>SER_FI_THL_TTR_140</t>
         </is>
       </c>
       <c r="AT136" t="n">
@@ -28508,47 +28505,47 @@
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -28580,12 +28577,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -28619,29 +28616,29 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O137" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_202_MONTHLY</t>
+          <t>SER_FI_THL_TTR_140</t>
         </is>
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_202_MONTHLY</t>
+          <t>SER_FI_THL_TTR_140</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>Hepatitt B, akutt</t>
+          <t>Hepatitis B, acute</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
@@ -28666,7 +28663,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr">
@@ -28701,17 +28698,17 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS acute category.</t>
+          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -28729,12 +28726,12 @@
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_202_MONTHLY</t>
+          <t>SER_FI_THL_TTR_140</t>
         </is>
       </c>
       <c r="AT137" t="n">
@@ -28742,47 +28739,47 @@
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -28814,12 +28811,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -28853,13 +28850,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O138" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R138" t="n">
-        <v>0.03041984712505827</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -28868,7 +28865,7 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
+          <t>SER_NO_FHI_202_MONTHLY</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -28893,7 +28890,7 @@
       </c>
       <c r="AS138" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
+          <t>SER_NO_FHI_202_MONTHLY</t>
         </is>
       </c>
       <c r="AT138" t="n">
@@ -28906,42 +28903,42 @@
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28973,12 +28970,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -29012,29 +29009,29 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O139" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
+          <t>SER_NO_FHI_202_MONTHLY</t>
         </is>
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
+          <t>SER_NO_FHI_202_MONTHLY</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>急性病毒性Ｂ型肝炎</t>
+          <t>Hepatitt B, akutt</t>
         </is>
       </c>
       <c r="Y139" t="inlineStr">
@@ -29044,7 +29041,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -29059,7 +29056,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD139" t="inlineStr">
@@ -29074,7 +29071,7 @@
       </c>
       <c r="AF139" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG139" t="inlineStr">
@@ -29094,17 +29091,17 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>Acute hepatitis B, code 0703.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS acute category.</t>
         </is>
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -29127,7 +29124,7 @@
       </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
+          <t>SER_NO_FHI_202_MONTHLY</t>
         </is>
       </c>
       <c r="AT139" t="n">
@@ -29140,42 +29137,42 @@
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -29207,12 +29204,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -29237,7 +29234,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -29246,16 +29243,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="O140" t="n">
-        <v>14</v>
-      </c>
-      <c r="P140" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R140" t="n">
-        <v>0.00401105338587714</v>
+        <v>0.03041984712505827</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -29264,85 +29258,80 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ140" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
         </is>
       </c>
       <c r="AT140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -29374,12 +29363,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -29404,7 +29393,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -29413,32 +29402,29 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="O141" t="n">
-        <v>14</v>
-      </c>
-      <c r="P141" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
         </is>
       </c>
       <c r="V141" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>Hepatitis B, acute, Confirmed</t>
+          <t>急性病毒性Ｂ型肝炎</t>
         </is>
       </c>
       <c r="Y141" t="inlineStr">
@@ -29453,7 +29439,7 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
@@ -29463,7 +29449,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD141" t="inlineStr">
@@ -29503,12 +29489,12 @@
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+          <t>Acute hepatitis B, code 0703.</t>
         </is>
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -29516,75 +29502,70 @@
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
         </is>
       </c>
       <c r="AT141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -29611,7 +29592,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -29655,106 +29636,31 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="O142" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="P142" t="n">
-        <v>5</v>
+        <v>14</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.00401105338587714</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V142" t="inlineStr">
-        <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>Hepatitis B, acute, Probable</t>
-        </is>
-      </c>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD142" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE142" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF142" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG142" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH142" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ142" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK142" t="inlineStr">
-        <is>
-          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
-        </is>
-      </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN142" t="b">
-        <v>0</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
@@ -29853,7 +29759,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -29888,7 +29794,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -29897,31 +29803,106 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O143" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P143" t="n">
-        <v>15</v>
-      </c>
-      <c r="R143" t="n">
-        <v>0.004297557199154077</v>
-      </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>14</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
           <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN143" t="b">
+        <v>1</v>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
@@ -30055,7 +30036,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -30064,22 +30045,22 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O144" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="P144" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V144" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
@@ -30089,7 +30070,7 @@
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>Hepatitis B, acute, Confirmed</t>
+          <t>Hepatitis B, acute, Probable</t>
         </is>
       </c>
       <c r="Y144" t="inlineStr">
@@ -30154,7 +30135,7 @@
       </c>
       <c r="AK144" t="inlineStr">
         <is>
-          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
         </is>
       </c>
       <c r="AM144" t="inlineStr">
@@ -30163,7 +30144,7 @@
         </is>
       </c>
       <c r="AN144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
@@ -30262,7 +30243,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -30306,106 +30287,31 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O145" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="P145" t="n">
-        <v>7</v>
+        <v>15</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0.004297557199154077</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V145" t="inlineStr">
-        <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W145" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X145" t="inlineStr">
-        <is>
-          <t>Hepatitis B, acute, Probable</t>
-        </is>
-      </c>
-      <c r="Y145" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD145" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE145" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF145" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG145" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
-        </is>
-      </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN145" t="b">
-        <v>0</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
@@ -30504,7 +30410,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -30539,7 +30445,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -30548,31 +30454,106 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="O146" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="P146" t="n">
-        <v>25</v>
-      </c>
-      <c r="R146" t="n">
-        <v>0.007162595331923463</v>
-      </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>15</v>
       </c>
       <c r="U146" t="inlineStr">
         <is>
           <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN146" t="b">
+        <v>1</v>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
@@ -30706,7 +30687,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -30715,22 +30696,22 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="O147" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="P147" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
@@ -30740,7 +30721,7 @@
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>Hepatitis B, acute, Confirmed</t>
+          <t>Hepatitis B, acute, Probable</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
@@ -30805,7 +30786,7 @@
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
@@ -30814,7 +30795,7 @@
         </is>
       </c>
       <c r="AN147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
@@ -30913,7 +30894,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -30957,106 +30938,31 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="O148" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="P148" t="n">
-        <v>7</v>
+        <v>25</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0.007162595331923463</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V148" t="inlineStr">
-        <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W148" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>Hepatitis B, acute, Probable</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD148" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE148" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF148" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG148" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH148" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI148" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
-        </is>
-      </c>
-      <c r="AM148" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN148" t="b">
-        <v>0</v>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
@@ -31155,7 +31061,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -31190,7 +31096,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -31199,31 +31105,106 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O149" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P149" t="n">
-        <v>23</v>
-      </c>
-      <c r="R149" t="n">
-        <v>0.006589587705369587</v>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>25</v>
       </c>
       <c r="U149" t="inlineStr">
         <is>
           <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN149" t="b">
+        <v>1</v>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
@@ -31357,7 +31338,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -31366,22 +31347,22 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="O150" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="P150" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V150" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
@@ -31391,7 +31372,7 @@
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>Hepatitis B, acute, Confirmed</t>
+          <t>Hepatitis B, acute, Probable</t>
         </is>
       </c>
       <c r="Y150" t="inlineStr">
@@ -31456,7 +31437,7 @@
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
         </is>
       </c>
       <c r="AM150" t="inlineStr">
@@ -31465,7 +31446,7 @@
         </is>
       </c>
       <c r="AN150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
@@ -31564,7 +31545,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -31608,106 +31589,31 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="O151" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="P151" t="n">
-        <v>6</v>
+        <v>23</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0.006589587705369587</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V151" t="inlineStr">
-        <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W151" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>Hepatitis B, acute, Probable</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD151" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE151" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF151" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG151" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN151" t="b">
-        <v>0</v>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
@@ -31806,17 +31712,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -31841,37 +31747,115 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O152" t="n">
-        <v>0</v>
-      </c>
-      <c r="R152" t="n">
-        <v>0</v>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>23</v>
+      </c>
+      <c r="P152" t="n">
+        <v>23</v>
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_NEW</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN152" t="b">
+        <v>1</v>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
@@ -31880,7 +31864,7 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
@@ -31888,57 +31872,62 @@
           <t>legacy_gap_fill</t>
         </is>
       </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_NEW</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AT152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -31970,12 +31959,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -32000,113 +31989,116 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N153" t="n">
+        <v>6</v>
+      </c>
+      <c r="O153" t="n">
+        <v>6</v>
+      </c>
+      <c r="P153" t="n">
+        <v>6</v>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Probable</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN153" t="b">
         <v>0</v>
       </c>
-      <c r="O153" t="n">
-        <v>0</v>
-      </c>
-      <c r="U153" t="inlineStr">
-        <is>
-          <t>SER_AU_HEPATITIS_B_NEW</t>
-        </is>
-      </c>
-      <c r="V153" t="inlineStr">
-        <is>
-          <t>SER_AU_HEPATITIS_B_NEW</t>
-        </is>
-      </c>
-      <c r="W153" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>Hepatitis B (newly acquired)</t>
-        </is>
-      </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA153" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD153" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE153" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF153" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG153" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ153" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK153" t="inlineStr">
-        <is>
-          <t>Newly acquired hepatitis B, separate from unspecified hepatitis B.</t>
-        </is>
-      </c>
-      <c r="AM153" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN153" t="b">
-        <v>1</v>
-      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>mixed</t>
@@ -32114,7 +32106,7 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ153" t="inlineStr">
@@ -32122,57 +32114,62 @@
           <t>legacy_gap_fill</t>
         </is>
       </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_NEW</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AT153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -32204,12 +32201,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -32258,7 +32255,7 @@
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_140</t>
+          <t>SER_AU_HEPATITIS_B_NEW</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -32268,7 +32265,7 @@
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
@@ -32278,12 +32275,12 @@
       </c>
       <c r="AQ154" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_140</t>
+          <t>SER_AU_HEPATITIS_B_NEW</t>
         </is>
       </c>
       <c r="AT154" t="n">
@@ -32291,47 +32288,47 @@
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -32363,12 +32360,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -32409,22 +32406,22 @@
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_140</t>
+          <t>SER_AU_HEPATITIS_B_NEW</t>
         </is>
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_140</t>
+          <t>SER_AU_HEPATITIS_B_NEW</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_AU_NINDSS</t>
         </is>
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>Hepatitis B, acute</t>
+          <t>Hepatitis B (newly acquired)</t>
         </is>
       </c>
       <c r="Y155" t="inlineStr">
@@ -32434,7 +32431,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -32449,7 +32446,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:AU:national</t>
         </is>
       </c>
       <c r="AD155" t="inlineStr">
@@ -32464,7 +32461,7 @@
       </c>
       <c r="AF155" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG155" t="inlineStr">
@@ -32484,17 +32481,17 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
+          <t>Newly acquired hepatitis B, separate from unspecified hepatitis B.</t>
         </is>
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -32502,7 +32499,7 @@
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
@@ -32512,12 +32509,12 @@
       </c>
       <c r="AQ155" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_140</t>
+          <t>SER_AU_HEPATITIS_B_NEW</t>
         </is>
       </c>
       <c r="AT155" t="n">
@@ -32525,47 +32522,47 @@
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -32597,12 +32594,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -32651,7 +32648,7 @@
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_202_MONTHLY</t>
+          <t>SER_FI_THL_TTR_140</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -32671,12 +32668,12 @@
       </c>
       <c r="AQ156" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_202_MONTHLY</t>
+          <t>SER_FI_THL_TTR_140</t>
         </is>
       </c>
       <c r="AT156" t="n">
@@ -32684,47 +32681,47 @@
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -32756,12 +32753,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -32802,22 +32799,22 @@
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_202_MONTHLY</t>
+          <t>SER_FI_THL_TTR_140</t>
         </is>
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_202_MONTHLY</t>
+          <t>SER_FI_THL_TTR_140</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>Hepatitt B, akutt</t>
+          <t>Hepatitis B, acute</t>
         </is>
       </c>
       <c r="Y157" t="inlineStr">
@@ -32842,7 +32839,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD157" t="inlineStr">
@@ -32877,17 +32874,17 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS acute category.</t>
+          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
         </is>
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32905,12 +32902,12 @@
       </c>
       <c r="AQ157" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_202_MONTHLY</t>
+          <t>SER_FI_THL_TTR_140</t>
         </is>
       </c>
       <c r="AT157" t="n">
@@ -32918,47 +32915,47 @@
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -32990,12 +32987,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -33029,13 +33026,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>0.01738276978574758</v>
+        <v>0</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -33044,7 +33041,7 @@
       </c>
       <c r="U158" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
+          <t>SER_NO_FHI_202_MONTHLY</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -33069,7 +33066,7 @@
       </c>
       <c r="AS158" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
+          <t>SER_NO_FHI_202_MONTHLY</t>
         </is>
       </c>
       <c r="AT158" t="n">
@@ -33082,42 +33079,42 @@
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -33149,12 +33146,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -33188,29 +33185,29 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
+          <t>SER_NO_FHI_202_MONTHLY</t>
         </is>
       </c>
       <c r="V159" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
+          <t>SER_NO_FHI_202_MONTHLY</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X159" t="inlineStr">
         <is>
-          <t>急性病毒性Ｂ型肝炎</t>
+          <t>Hepatitt B, akutt</t>
         </is>
       </c>
       <c r="Y159" t="inlineStr">
@@ -33220,7 +33217,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -33235,7 +33232,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD159" t="inlineStr">
@@ -33250,7 +33247,7 @@
       </c>
       <c r="AF159" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG159" t="inlineStr">
@@ -33270,17 +33267,17 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
         <is>
-          <t>Acute hepatitis B, code 0703.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS acute category.</t>
         </is>
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -33303,7 +33300,7 @@
       </c>
       <c r="AS159" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
+          <t>SER_NO_FHI_202_MONTHLY</t>
         </is>
       </c>
       <c r="AT159" t="n">
@@ -33316,42 +33313,42 @@
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -33383,12 +33380,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -33422,16 +33419,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="O160" t="n">
-        <v>18</v>
-      </c>
-      <c r="P160" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="R160" t="n">
-        <v>0.005157068638984894</v>
+        <v>0.01738276978574758</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -33440,85 +33434,80 @@
       </c>
       <c r="U160" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ160" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
         </is>
       </c>
       <c r="AT160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -33550,12 +33539,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -33589,32 +33578,29 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="O161" t="n">
-        <v>18</v>
-      </c>
-      <c r="P161" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
         </is>
       </c>
       <c r="V161" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>Hepatitis B, acute, Confirmed</t>
+          <t>急性病毒性Ｂ型肝炎</t>
         </is>
       </c>
       <c r="Y161" t="inlineStr">
@@ -33629,7 +33615,7 @@
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr">
@@ -33639,7 +33625,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD161" t="inlineStr">
@@ -33679,12 +33665,12 @@
       </c>
       <c r="AK161" t="inlineStr">
         <is>
-          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+          <t>Acute hepatitis B, code 0703.</t>
         </is>
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -33692,75 +33678,70 @@
       </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ161" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
         </is>
       </c>
       <c r="AT161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -33787,7 +33768,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -33831,106 +33812,31 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="O162" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="P162" t="n">
-        <v>3</v>
+        <v>18</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0.005157068638984894</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W162" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>Hepatitis B, acute, Probable</t>
-        </is>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD162" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE162" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF162" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG162" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN162" t="b">
-        <v>0</v>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
@@ -34029,7 +33935,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -34064,7 +33970,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -34073,31 +33979,106 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O163" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="P163" t="n">
-        <v>13</v>
-      </c>
-      <c r="R163" t="n">
-        <v>0.003724549572600201</v>
-      </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>18</v>
       </c>
       <c r="U163" t="inlineStr">
         <is>
           <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN163" t="b">
+        <v>1</v>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
@@ -34231,7 +34212,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -34240,22 +34221,22 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O164" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="P164" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V164" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
@@ -34265,7 +34246,7 @@
       </c>
       <c r="X164" t="inlineStr">
         <is>
-          <t>Hepatitis B, acute, Confirmed</t>
+          <t>Hepatitis B, acute, Probable</t>
         </is>
       </c>
       <c r="Y164" t="inlineStr">
@@ -34330,7 +34311,7 @@
       </c>
       <c r="AK164" t="inlineStr">
         <is>
-          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
         </is>
       </c>
       <c r="AM164" t="inlineStr">
@@ -34339,7 +34320,7 @@
         </is>
       </c>
       <c r="AN164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO164" t="inlineStr">
         <is>
@@ -34438,7 +34419,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -34482,106 +34463,31 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O165" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="P165" t="n">
-        <v>2</v>
+        <v>13</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0.003724549572600201</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V165" t="inlineStr">
-        <is>
-          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W165" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>Hepatitis B, acute, Probable</t>
-        </is>
-      </c>
-      <c r="Y165" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD165" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE165" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF165" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG165" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH165" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI165" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN165" t="b">
-        <v>0</v>
       </c>
       <c r="AO165" t="inlineStr">
         <is>
@@ -34652,6 +34558,490 @@
         </is>
       </c>
       <c r="BC165" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>13</v>
+      </c>
+      <c r="O166" t="n">
+        <v>13</v>
+      </c>
+      <c r="P166" t="n">
+        <v>13</v>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN166" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>2</v>
+      </c>
+      <c r="O167" t="n">
+        <v>2</v>
+      </c>
+      <c r="P167" t="n">
+        <v>2</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Probable</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -34773,7 +35163,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -34783,7 +35173,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -34803,7 +35193,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -34835,7 +35225,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>681</v>
+        <v>692</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -32633,13 +32633,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -32792,10 +32792,10 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
@@ -35225,7 +35225,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -23749,7 +23749,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -28315,7 +28315,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -32491,7 +32491,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN155" t="b">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -32633,13 +32633,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R156" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -32792,10 +32792,10 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
@@ -35042,6 +35042,657 @@
         </is>
       </c>
       <c r="BC167" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>14</v>
+      </c>
+      <c r="O168" t="n">
+        <v>14</v>
+      </c>
+      <c r="P168" t="n">
+        <v>14</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0.00401105338587714</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>14</v>
+      </c>
+      <c r="O169" t="n">
+        <v>14</v>
+      </c>
+      <c r="P169" t="n">
+        <v>14</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN169" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA169" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB169" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC169" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>3</v>
+      </c>
+      <c r="O170" t="n">
+        <v>3</v>
+      </c>
+      <c r="P170" t="n">
+        <v>3</v>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Probable</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -35080,7 +35731,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -35163,7 +35814,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -35173,7 +35824,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -35193,7 +35844,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -35225,7 +35876,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>693</v>
+        <v>708</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -32633,13 +32633,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R156" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -32792,10 +32792,10 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -32633,13 +32633,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O156" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R156" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -32792,10 +32792,10 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O157" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -12598,7 +12598,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -15619,7 +15619,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16664,7 +16664,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -17467,7 +17467,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -17709,7 +17709,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18512,7 +18512,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18754,7 +18754,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -20881,7 +20881,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21527,7 +21527,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -22572,7 +22572,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23375,7 +23375,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23617,7 +23617,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24420,7 +24420,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24662,7 +24662,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -26789,7 +26789,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -27193,7 +27193,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -27435,7 +27435,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -28238,7 +28238,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28480,7 +28480,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29283,7 +29283,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -29525,7 +29525,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -30328,7 +30328,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30570,7 +30570,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -31373,7 +31373,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -31615,7 +31615,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -32407,7 +32407,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -33976,7 +33976,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34380,7 +34380,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34622,7 +34622,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -35667,7 +35667,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -36470,7 +36470,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36712,7 +36712,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -37515,7 +37515,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -37757,7 +37757,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -38549,7 +38549,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -39728,7 +39728,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -40132,7 +40132,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40374,7 +40374,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -41177,7 +41177,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -41419,7 +41419,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -42222,7 +42222,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -42464,7 +42464,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -43267,7 +43267,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -43509,7 +43509,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -44301,7 +44301,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -45884,7 +45884,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -46126,7 +46126,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -47171,7 +47171,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -47974,7 +47974,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -48216,7 +48216,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -49019,7 +49019,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -49261,7 +49261,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -12598,7 +12598,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -15619,7 +15619,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16664,7 +16664,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -17467,7 +17467,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -17709,7 +17709,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18512,7 +18512,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18754,7 +18754,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -20881,7 +20881,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21527,7 +21527,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -22572,7 +22572,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23375,7 +23375,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23617,7 +23617,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24420,7 +24420,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24662,7 +24662,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -26789,7 +26789,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -27193,7 +27193,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -27435,7 +27435,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -28238,7 +28238,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28480,7 +28480,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29283,7 +29283,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -29525,7 +29525,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -30328,7 +30328,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30570,7 +30570,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -31373,7 +31373,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -31615,7 +31615,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -32407,7 +32407,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -33976,7 +33976,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34380,7 +34380,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34622,7 +34622,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -35667,7 +35667,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -36470,7 +36470,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36712,7 +36712,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -37515,7 +37515,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -37757,7 +37757,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -38549,7 +38549,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -39728,7 +39728,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -40132,7 +40132,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40374,7 +40374,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -41177,7 +41177,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -41419,7 +41419,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -42222,7 +42222,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -42464,7 +42464,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -43267,7 +43267,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -43509,7 +43509,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -44301,7 +44301,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -45884,7 +45884,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -46126,7 +46126,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -47171,7 +47171,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -47974,7 +47974,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -48216,7 +48216,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -49019,7 +49019,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -49261,7 +49261,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -12598,7 +12598,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -15619,7 +15619,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16664,7 +16664,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -17467,7 +17467,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -17709,7 +17709,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18512,7 +18512,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18754,7 +18754,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -20881,7 +20881,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21527,7 +21527,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -22572,7 +22572,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23375,7 +23375,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23617,7 +23617,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24420,7 +24420,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24662,7 +24662,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -26789,7 +26789,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -27193,7 +27193,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -27435,7 +27435,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -28238,7 +28238,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28480,7 +28480,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29283,7 +29283,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -29525,7 +29525,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -30328,7 +30328,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30570,7 +30570,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -31373,7 +31373,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -31615,7 +31615,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -32407,7 +32407,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -33976,7 +33976,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34380,7 +34380,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34622,7 +34622,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -35667,7 +35667,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -36470,7 +36470,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36712,7 +36712,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -37515,7 +37515,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -37757,7 +37757,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -38549,7 +38549,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -39728,7 +39728,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -40132,7 +40132,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40374,7 +40374,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -41177,7 +41177,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -41419,7 +41419,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -42222,7 +42222,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -42464,7 +42464,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -43267,7 +43267,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -43509,7 +43509,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -44301,7 +44301,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -45884,7 +45884,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -46126,7 +46126,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -46929,7 +46929,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -47171,7 +47171,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -47974,7 +47974,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -48216,7 +48216,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -49019,7 +49019,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -49261,7 +49261,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -47151,13 +47151,13 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O235" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R235" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
@@ -47310,10 +47310,10 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O236" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U236" t="inlineStr">
         <is>
@@ -53161,13 +53161,13 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R264" t="n">
-        <v>0</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
@@ -53320,10 +53320,10 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O265" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U265" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>771</v>
+        <v>773</v>
       </c>
     </row>
     <row r="16">
